--- a/007/xy_007_data.xlsx
+++ b/007/xy_007_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>

--- a/007/xy_007_data.xlsx
+++ b/007/xy_007_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C214"/>
+  <dimension ref="A1:C213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3146,17 +3146,6 @@
       </c>
       <c r="C213" t="n">
         <v>7711.323335193452</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B214" t="n">
-        <v>6.743018749999999</v>
-      </c>
-      <c r="C214" t="n">
-        <v>7658.973754882812</v>
       </c>
     </row>
   </sheetData>
@@ -10600,7 +10589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B214"/>
+  <dimension ref="A1:B213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12313,14 +12302,6 @@
       </c>
       <c r="B213" t="n">
         <v>7711.323335193452</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B214" t="n">
-        <v>7658.973754882812</v>
       </c>
     </row>
   </sheetData>
@@ -12382,14 +12363,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>653.523, -295.867</t>
+          <t>647.19, -280.577</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6319</v>
+        <v>0.6395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6302</v>
+        <v>0.6378</v>
       </c>
     </row>
     <row r="3">
@@ -12403,14 +12384,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-103.136, 1778.43, -2888.96</t>
+          <t>-99.957, 1737.95, -2795.01</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6822</v>
+        <v>0.6883</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6792</v>
+        <v>0.6853</v>
       </c>
     </row>
     <row r="4">
@@ -12424,14 +12405,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-74.1473, 1082.74, -3962.26, 5392.53</t>
+          <t>-71.8832, 1048.98, -3818.28, 5212.32</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7806</v>
+        <v>0.7831</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7775</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="5">
@@ -12445,14 +12426,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.21524, -189.038, 1970.27, -6766.87, 8412.51</t>
+          <t>4.76022, -176.767, 1859.34, -6379.26, 7970.15</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7815</v>
+        <v>0.7839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7773</v>
+        <v>0.7796999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -12469,7 +12450,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -12482,7 +12463,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7997</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -12495,7 +12476,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.115229707796577e-47</v>
+        <v>2.042655130682028e-48</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -12508,7 +12489,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.460051051802382e-16</v>
+        <v>9.894051655061307e-17</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -12522,7 +12503,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>y = 654x - 296</t>
+          <t>y = 647x - 281</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>

--- a/007/xy_007_data.xlsx
+++ b/007/xy_007_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Overfit Special</t>
+          <t>Fed Balance Sheet vs S&amp;P 500</t>
         </is>
       </c>
     </row>
@@ -488,293 +488,281 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Fed's balance sheet explains the stock market. With enough polynomial terms, anything does.</t>
+          <t>Stocks rise with the Fed's balance sheet.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Two trending series will always look related. Treat with caution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>publication</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://xandyregression.substack.com</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fed total assets ($tn, FRED)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X label</t>
+          <t>X detail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fed total assets ($tn, FRED)</t>
+          <t>Federal Reserve total assets, $ trillion, weekly averaged to monthly, FRED WALCL, 2009 - present</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X detail</t>
+          <t>X source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Federal Reserve total assets, $ trillion, weekly averaged to monthly, FRED WALCL, 2009 - present</t>
+          <t>FRED WALCL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X source</t>
+          <t>X source URL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FRED WALCL</t>
+          <t>https://fred.stlouisfed.org/series/WALCL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X source URL</t>
+          <t>X licence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/series/WALCL</t>
+          <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X licence</t>
+          <t>X pulled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>open data, redistributed with attribution</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X pulled</t>
+          <t>X steps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>multiplied by 1e-06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X steps</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>multiplied by 1e-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>X raw sheet</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>full series as pulled, before any transform</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Y label</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (monthly avg close)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y label</t>
+          <t>Y detail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S&amp;P 500 (monthly avg close)</t>
+          <t>S&amp;P 500 index, daily close averaged by month, Yahoo Finance ^GSPC, 2009 - present</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y detail</t>
+          <t>Y source</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S&amp;P 500 index, daily close averaged by month, Yahoo Finance ^GSPC, 2009 - present</t>
+          <t>Yahoo Finance ^GSPC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y source</t>
+          <t>Y source URL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yahoo Finance ^GSPC</t>
+          <t>https://finance.yahoo.com/quote/^GSPC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y source URL</t>
+          <t>Y licence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/quote/^GSPC</t>
+          <t>third-party data: only the aggregated values used are included, see source</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y licence</t>
+          <t>Y pulled</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>third-party data: only the aggregated values used are included, see source</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y pulled</t>
+          <t>Y steps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y steps</t>
+          <t>Y raw sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>values used in the regression only (source licence); full series at source URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>join</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>resampled to M by mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>lag</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>X leads Y by 0 periods</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Y raw sheet</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>values used in the regression only (source licence); full series at source URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>join</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>resampled to M by mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>lag</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>X leads Y by 0 periods</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Newey-West (HAC) for time series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Newey-West (HAC) for time series</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
